--- a/model_templates/ark.SnRNASeqProcessedDataAnnotationTemplate.xlsx
+++ b/model_templates/ark.SnRNASeqProcessedDataAnnotationTemplate.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -25072,7 +25072,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
   <si>
     <t>Component</t>
   </si>
@@ -25180,6 +25180,9 @@
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>unknown</t>
   </si>
   <si>
     <t>filtered_peak_bc_matrix</t>
@@ -25487,6 +25490,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
@@ -52738,24 +52745,24 @@
       <c r="Y1000" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J1:J1000">
+  <conditionalFormatting sqref="I1:I1000">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$F1 = "single specimen"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1000">
+  <conditionalFormatting sqref="J1:J1000">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
       <formula>$F1 = "single specimen"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
-      <formula>$D1 = "experimental data"</formula>
+  <conditionalFormatting sqref="K1:K1000">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$D1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K1000">
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
-      <formula>$D1 = "metadata"</formula>
+  <conditionalFormatting sqref="L1:L1000">
+    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
+      <formula>$D1 = "experimental data"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1000">
@@ -52788,11 +52795,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
       <formula1>Sheet2!$H$2:$H$10</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="F2:F1000">
+      <formula1>Sheet2!$F$2:$F$4</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="E2:E1000">
       <formula1>Sheet2!$E$2:$E$6</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="F2:F1000">
-      <formula1>Sheet2!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="G2:G1000">
       <formula1>Sheet2!$G$2:$G$8</formula1>
@@ -52922,247 +52929,250 @@
       <c r="E4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>38</v>
       </c>
+      <c r="L4" s="7" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
       <c r="C32" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34">
       <c r="C34" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35">
       <c r="C35" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/model_templates/ark.SnRNASeqProcessedDataAnnotationTemplate.xlsx
+++ b/model_templates/ark.SnRNASeqProcessedDataAnnotationTemplate.xlsx
@@ -52770,13 +52770,13 @@
       <formula>$C1 = "feature barcode sequencing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1000">
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+  <conditionalFormatting sqref="N1:N1000">
+    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
       <formula>$C1 = "feature barcode sequencing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1000">
-    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="M1:M1000">
+    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
       <formula>$C1 = "feature barcode sequencing"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/model_templates/ark.SnRNASeqProcessedDataAnnotationTemplate.xlsx
+++ b/model_templates/ark.SnRNASeqProcessedDataAnnotationTemplate.xlsx
@@ -52755,14 +52755,14 @@
       <formula>$F1 = "single specimen"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K1000">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$D1 = "metadata"</formula>
+  <conditionalFormatting sqref="L1:L1000">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+      <formula>$D1 = "experimental data"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1:L1000">
-    <cfRule type="expression" dxfId="1" priority="4" stopIfTrue="1">
-      <formula>$D1 = "experimental data"</formula>
+  <conditionalFormatting sqref="K1:K1000">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+      <formula>$D1 = "metadata"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1000">
@@ -52770,13 +52770,13 @@
       <formula>$C1 = "feature barcode sequencing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1000">
-    <cfRule type="expression" dxfId="1" priority="6" stopIfTrue="1">
+  <conditionalFormatting sqref="M1:M1000">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>$C1 = "feature barcode sequencing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1000">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="N1:N1000">
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
       <formula>$C1 = "feature barcode sequencing"</formula>
     </cfRule>
   </conditionalFormatting>
